--- a/data.xlsx
+++ b/data.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://grupoeducad-my.sharepoint.com/personal/jfrias_sise_edu_pe/Documents/Documentos/App/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JFRIAS\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="418" documentId="8_{6EF1BFC5-D881-4107-AB3D-98991DE92B01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{744E6866-8754-4810-9A14-85862DB944D1}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51F2208C-F1C8-45B9-B4DD-6F4B8E58A21E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{E90AC7BB-80C0-46C9-B9DE-3819E1FC9A7A}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="66">
   <si>
     <t>Inicio</t>
   </si>
@@ -227,10 +227,13 @@
     <t>9.1 Testing Funcional / Responsive</t>
   </si>
   <si>
-    <t>9.2 Levantamiento de Observaciones</t>
-  </si>
-  <si>
     <t>9.3 Deploy y Lanzamiento</t>
+  </si>
+  <si>
+    <t>9.2 Observaciones</t>
+  </si>
+  <si>
+    <t>9.4 Retroalimentación</t>
   </si>
 </sst>
 </file>
@@ -346,13 +349,9 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{8F81FDDC-5A21-4242-9C41-F2D87AEDDD98}" name="Gantt" displayName="Gantt" ref="A1:F46" totalsRowShown="0" headerRowDxfId="4" headerRowCellStyle="Bueno">
-  <autoFilter ref="A1:F46" xr:uid="{8F81FDDC-5A21-4242-9C41-F2D87AEDDD98}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{8F81FDDC-5A21-4242-9C41-F2D87AEDDD98}" name="Gantt" displayName="Gantt" ref="A1:F47" totalsRowShown="0" headerRowDxfId="4" headerRowCellStyle="Bueno">
+  <autoFilter ref="A1:F47" xr:uid="{8F81FDDC-5A21-4242-9C41-F2D87AEDDD98}"/>
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{55FDAEA2-01FB-4F5F-9014-7B1C7D456C4E}" name="Fase"/>
     <tableColumn id="7" xr3:uid="{1EF2853D-C3F9-4D00-BF1E-FA8122687325}" name="Actividad"/>
@@ -682,7 +681,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{23C9757E-19E6-4148-A64D-AFAD297119D4}">
-  <dimension ref="A1:F46"/>
+  <dimension ref="A1:F47"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="18" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="31.33203125" customWidth="1"/>
@@ -1010,7 +1009,7 @@
         <v>8</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -1030,7 +1029,7 @@
         <v>8</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -1050,7 +1049,7 @@
         <v>8</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -1070,7 +1069,7 @@
         <v>10</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -1090,7 +1089,7 @@
         <v>9</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -1110,7 +1109,7 @@
         <v>8</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -1130,7 +1129,7 @@
         <v>8</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -1150,7 +1149,7 @@
         <v>8</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -1170,7 +1169,7 @@
         <v>8</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -1190,7 +1189,7 @@
         <v>10</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -1578,13 +1577,13 @@
         <v>18</v>
       </c>
       <c r="B45" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C45" s="2">
         <v>46207</v>
       </c>
       <c r="D45" s="2">
-        <v>46210</v>
+        <v>46218</v>
       </c>
       <c r="E45" s="3" t="s">
         <v>8</v>
@@ -1598,18 +1597,38 @@
         <v>18</v>
       </c>
       <c r="B46" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C46" s="2">
-        <v>46211</v>
+        <v>46219</v>
       </c>
       <c r="D46" s="2">
-        <v>46213</v>
+        <v>46234</v>
       </c>
       <c r="E46" s="3" t="s">
         <v>9</v>
       </c>
       <c r="F46" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>18</v>
+      </c>
+      <c r="B47" t="s">
+        <v>65</v>
+      </c>
+      <c r="C47" s="2">
+        <v>46235</v>
+      </c>
+      <c r="D47" s="2">
+        <v>46251</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F47" s="3" t="s">
         <v>5</v>
       </c>
     </row>
